--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -817,6 +817,336 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:37</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr"/>
+      <c r="E8" t="inlineStr"/>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9b890c62f1d70526391270e50253c706_1788025012.mp4</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:40</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr"/>
+      <c r="E9" t="inlineStr"/>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/8aec8fa68897dff552e602f569e654aa_1788025168.mp4</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:42</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr"/>
+      <c r="E10" t="inlineStr"/>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr"/>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/63bc56e064f007f55eccc6873a31db42_1788025327.mp4</t>
+        </is>
+      </c>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:45</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr"/>
+      <c r="E11" t="inlineStr"/>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr"/>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0935fc8f4bdf03a9a33bc4df67e789a9_1788025486.mp4</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:47</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr"/>
+      <c r="E12" t="inlineStr"/>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr"/>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ba234cfbd25f8343f5828c4402e08dfe_1788025643.mp4</t>
+        </is>
+      </c>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-08-29 17:50</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr"/>
+      <c r="E13" t="inlineStr"/>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr"/>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9d021305184ad9778a58fe69df373383_1788025809.mp4</t>
+        </is>
+      </c>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:M19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1147,6 +1147,336 @@
         </is>
       </c>
     </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:41</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr"/>
+      <c r="E14" t="inlineStr"/>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr"/>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/933891fee9d9e9517a7d1352abf0c99d_1788028847.mp4</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:44</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr"/>
+      <c r="E15" t="inlineStr"/>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr"/>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d465f00f7e8ea99ab4f6e8af0e777a67_1788029028.mp4</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:46</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr"/>
+      <c r="E16" t="inlineStr"/>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr"/>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/4261a624691bea465903fda86f5909c9_1788029186.mp4</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:49</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr"/>
+      <c r="E17" t="inlineStr"/>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr"/>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/afb9a6468d483f531af7e0f85ec72c68_1788029358.mp4</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:52</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr"/>
+      <c r="E18" t="inlineStr"/>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/502cad3dd5d6c6734f6a894bf84b6030_1788029550.mp4</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-08-29 18:55</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr"/>
+      <c r="E19" t="inlineStr"/>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr"/>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a161e6df7599199a59f818aa1306883b_1788029710.mp4</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M19"/>
+  <dimension ref="A1:M25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1477,6 +1477,336 @@
         </is>
       </c>
     </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:19</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr"/>
+      <c r="E20" t="inlineStr"/>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr"/>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1ca795881ec2378d2aecaab3453c8c14_1788031153.mp4</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:22</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr"/>
+      <c r="E21" t="inlineStr"/>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr"/>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/39bcd85b1eb3bb65996d61237b5fb849_1788031338.mp4</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:26</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr"/>
+      <c r="E22" t="inlineStr"/>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr"/>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/1763f4837138938766dbecd39d467b98_1788031548.mp4</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:29</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr"/>
+      <c r="E23" t="inlineStr"/>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr"/>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/be9211d742b6a7ff693250c3127e3ddb_1788031716.mp4</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:32</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr"/>
+      <c r="E24" t="inlineStr"/>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr"/>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K24" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L24" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/527c4edac2c7ba82201eb00c1fde2199_1788031909.mp4</t>
+        </is>
+      </c>
+      <c r="M24" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:34</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr"/>
+      <c r="E25" t="inlineStr"/>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr"/>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K25" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L25" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/976a57a1843431e8aa3380276a474f36_1788032067.mp4</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M25"/>
+  <dimension ref="A1:M31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1807,6 +1807,336 @@
         </is>
       </c>
     </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:48</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr"/>
+      <c r="E26" t="inlineStr"/>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr"/>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K26" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L26" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6eefd2fa1c221265277779856721c5a3_1788032863.mp4</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:50</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr"/>
+      <c r="E27" t="inlineStr"/>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b04c53575c1816806db1c1a84a475817_1788033037.mp4</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:53</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr"/>
+      <c r="E28" t="inlineStr"/>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr"/>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/51fea1aeb52286311bd55f72dc6f5a1f_1788033178.mp4</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:56</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr"/>
+      <c r="E29" t="inlineStr"/>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr"/>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7780204878917d09d07c19c3a1e273c3_1788033345.mp4</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>2026-08-29 19:58</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr"/>
+      <c r="E30" t="inlineStr"/>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr"/>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d448b2a54898c9af9c2cd36c2debace0_1788033486.mp4</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>2026-08-29 20:01</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr"/>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr"/>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9e0e60859f2d7c83c16ad2e3c869051c_1788033650.mp4</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep01/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M31"/>
+  <dimension ref="A1:M37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2137,6 +2137,336 @@
         </is>
       </c>
     </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:39</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr"/>
+      <c r="E32" t="inlineStr"/>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr"/>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L32" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/36eb07ccfe1d76cd4d844468e589de50_1788111549.mp4</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:42</t>
+        </is>
+      </c>
+      <c r="B33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr"/>
+      <c r="E33" t="inlineStr"/>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr"/>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L33" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d7f2e86abed83b176db5347c2eacd2b6_1788111704.mp4</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:44</t>
+        </is>
+      </c>
+      <c r="B34" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr"/>
+      <c r="E34" t="inlineStr"/>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr"/>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L34" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/480167bd20704be48a72ecc5d0cdbced_1788111858.mp4</t>
+        </is>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:47</t>
+        </is>
+      </c>
+      <c r="B35" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr"/>
+      <c r="E35" t="inlineStr"/>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr"/>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L35" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2383ea9b88d49e2e939e547612b960d0_1788112039.mp4</t>
+        </is>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:50</t>
+        </is>
+      </c>
+      <c r="B36" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr"/>
+      <c r="E36" t="inlineStr"/>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr"/>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L36" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/3842844c1a108f51492d1053139e77e9_1788112184.mp4</t>
+        </is>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="inlineStr">
+        <is>
+          <t>2026-08-30 17:52</t>
+        </is>
+      </c>
+      <c r="B37" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr"/>
+      <c r="E37" t="inlineStr"/>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr"/>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L37" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/eb8627508b11173d46dafaf9246dcd77_1788112317.mp4</t>
+        </is>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep02/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M37"/>
+  <dimension ref="A1:M43"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2467,6 +2467,336 @@
         </is>
       </c>
     </row>
+    <row r="38">
+      <c r="A38" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:39</t>
+        </is>
+      </c>
+      <c r="B38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr"/>
+      <c r="E38" t="inlineStr"/>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr"/>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L38" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/96b4233b7425423168ada2cafad393a1_1788205154.mp4</t>
+        </is>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:41</t>
+        </is>
+      </c>
+      <c r="B39" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr"/>
+      <c r="E39" t="inlineStr"/>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr"/>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L39" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/7ec190eaabe06dd442f34d47f04491c4_1788205291.mp4</t>
+        </is>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:44</t>
+        </is>
+      </c>
+      <c r="B40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr"/>
+      <c r="E40" t="inlineStr"/>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr"/>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L40" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/b32d01cef784a26c2ccd4ebc5c244b6d_1788205416.mp4</t>
+        </is>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:46</t>
+        </is>
+      </c>
+      <c r="B41" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr"/>
+      <c r="E41" t="inlineStr"/>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr"/>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L41" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/2cf1c12264d4cfb6183fba441b89a17a_1788205541.mp4</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:48</t>
+        </is>
+      </c>
+      <c r="B42" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr"/>
+      <c r="E42" t="inlineStr"/>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr"/>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L42" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/29f5761265da332137b9153704dca9ae_1788205661.mp4</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="inlineStr">
+        <is>
+          <t>2026-08-31 19:50</t>
+        </is>
+      </c>
+      <c r="B43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr"/>
+      <c r="E43" t="inlineStr"/>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L43" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/5f3b7473f8632cb76354b2eb6beff553_1788205807.mp4</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep03/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M43"/>
+  <dimension ref="A1:M49"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2797,6 +2797,336 @@
         </is>
       </c>
     </row>
+    <row r="44">
+      <c r="A44" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:23</t>
+        </is>
+      </c>
+      <c r="B44" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr"/>
+      <c r="E44" t="inlineStr"/>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr"/>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L44" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/6f6d318371ac3ed6a058b835e925a4bc_1788283395.mp4</t>
+        </is>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:26</t>
+        </is>
+      </c>
+      <c r="B45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr"/>
+      <c r="E45" t="inlineStr"/>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L45" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9f4523579318719f40c37cdb8420722c_1788283535.mp4</t>
+        </is>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:28</t>
+        </is>
+      </c>
+      <c r="B46" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr"/>
+      <c r="E46" t="inlineStr"/>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L46" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/166bb466140e8e26139722ca3bed1262_1788283684.mp4</t>
+        </is>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:30</t>
+        </is>
+      </c>
+      <c r="B47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr"/>
+      <c r="E47" t="inlineStr"/>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr"/>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L47" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/541e4475f44d7bd3526a1c544dd51222_1788283817.mp4</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:33</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr"/>
+      <c r="E48" t="inlineStr"/>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr"/>
+      <c r="I48" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L48" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/0c732c1066b6225254d1de58e836eca6_1788283986.mp4</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>2026-09-01 17:37</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr"/>
+      <c r="E49" t="inlineStr"/>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr"/>
+      <c r="I49" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L49" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/23ba0c6241adc2c1781870188bea6c78_1788284198.mp4</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep04/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M49"/>
+  <dimension ref="A1:M56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3127,6 +3127,391 @@
         </is>
       </c>
     </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
+          <t>2026-09-02 17:52</t>
+        </is>
+      </c>
+      <c r="B50" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr"/>
+      <c r="E50" t="inlineStr"/>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L50" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/866270c84f83cb9bbc73e231b8704d48_1788371500.mp4</t>
+        </is>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:33</t>
+        </is>
+      </c>
+      <c r="B51" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr"/>
+      <c r="E51" t="inlineStr"/>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr"/>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L51" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e6c7d82114b1c91036bf79bfdf3882f4_1788381193.mp4</t>
+        </is>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:38</t>
+        </is>
+      </c>
+      <c r="B52" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C52" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D52" t="inlineStr"/>
+      <c r="E52" t="inlineStr"/>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J52" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K52" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L52" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/cc544de284283059cef65cc536634aee_1788381462.mp4</t>
+        </is>
+      </c>
+      <c r="M52" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:41</t>
+        </is>
+      </c>
+      <c r="B53" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C53" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D53" t="inlineStr"/>
+      <c r="E53" t="inlineStr"/>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr"/>
+      <c r="I53" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J53" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K53" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L53" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/a6b9cd9276f771f0f670ccb6146978bc_1788381660.mp4</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:44</t>
+        </is>
+      </c>
+      <c r="B54" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C54" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D54" t="inlineStr"/>
+      <c r="E54" t="inlineStr"/>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J54" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K54" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L54" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/9e597a4acaeafc6149aa3d6fb635fe9c_1788381826.mp4</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:48</t>
+        </is>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr"/>
+      <c r="E55" t="inlineStr"/>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr"/>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J55" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K55" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L55" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/ea4ca4771f06ab42ae79ac49b237a810_1788382054.mp4</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>2026-09-02 20:50</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D56" t="inlineStr"/>
+      <c r="E56" t="inlineStr"/>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J56" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K56" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L56" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/c3ef84b3b015406607f0da21802ebcd4_1788382217.mp4</t>
+        </is>
+      </c>
+      <c r="M56" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep05/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/aimagine/next-stop/series_log.xlsx
+++ b/aimagine/next-stop/series_log.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M56"/>
+  <dimension ref="A1:M62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -3512,6 +3512,336 @@
         </is>
       </c>
     </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:09</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D57" t="inlineStr"/>
+      <c r="E57" t="inlineStr"/>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr"/>
+      <c r="I57" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J57" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K57" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L57" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/130883cbd5220632d4ec7f952aaefa4c_1788455375.mp4</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_01.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:12</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D58" t="inlineStr"/>
+      <c r="E58" t="inlineStr"/>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K58" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L58" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/af9879d2a362e07a1899e0869019039f_1788455527.mp4</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_02.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:16</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D59" t="inlineStr"/>
+      <c r="E59" t="inlineStr"/>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J59" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/d957ba2e242fc998b8cf1af885649a73_1788455731.mp4</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_03.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:18</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D60" t="inlineStr"/>
+      <c r="E60" t="inlineStr"/>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J60" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L60" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/e81ef177f490d197ca602d9b44dfffcf_1788455888.mp4</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_04.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:21</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D61" t="inlineStr"/>
+      <c r="E61" t="inlineStr"/>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr"/>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/95639db820ceb49a5aa9dcb861aae430_1788456068.mp4</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_05.mp4</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>2026-09-03 17:24</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr"/>
+      <c r="E62" t="inlineStr"/>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>1080p</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>126.0</t>
+        </is>
+      </c>
+      <c r="J62" t="inlineStr">
+        <is>
+          <t>0.63</t>
+        </is>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>ok</t>
+        </is>
+      </c>
+      <c r="L62" t="inlineStr">
+        <is>
+          <t>https://tempfile.aiquickdraw.com/v/076d69b4cc49ae8a69ccba4ec05f80a6_1788456270.mp4</t>
+        </is>
+      </c>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>/home/runner/work/youtube-automation/youtube-automation/output/series/next-stop/episodes/ep06/shots/shot_06.mp4</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
